--- a/job_applications_sample.xlsx
+++ b/job_applications_sample.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{51711F79-1303-4BE6-9E8F-EF121C7F0B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ADBA5B4-F13D-4377-BE55-ECE33C9E8C69}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vacancies" sheetId="1" r:id="rId1"/>
